--- a/outputs/build/diagnostics/build_comparison.xlsx
+++ b/outputs/build/diagnostics/build_comparison.xlsx
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -227,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -249,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C7">
         <v>231</v>

--- a/outputs/build/diagnostics/build_comparison.xlsx
+++ b/outputs/build/diagnostics/build_comparison.xlsx
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -227,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -249,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C7">
         <v>231</v>
